--- a/main/ig/StructureDefinition-FRLMHeaderDocument.xlsx
+++ b/main/ig/StructureDefinition-FRLMHeaderDocument.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="152">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -453,6 +453,51 @@
   </si>
   <si>
     <t>Association du document à une prise en charge.</t>
+  </si>
+  <si>
+    <t>FRLMHeaderDocument.presentedForm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMAttachment
+</t>
+  </si>
+  <si>
+    <t>Pièces jointes (par exemple une version PDF du document).</t>
+  </si>
+  <si>
+    <t>FRLMHeaderDocument.documentReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
+</t>
+  </si>
+  <si>
+    <t>Document de référence (à remplacer, transformé, …).</t>
+  </si>
+  <si>
+    <t>FRLMHeaderDocument.documentReference.relationType</t>
+  </si>
+  <si>
+    <t>Nature de la relation avec le document cible (replaces | transforms | signs | appends).</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>(required): DocumentRelationshipType</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/document-relationship-type|4.0.1</t>
+  </si>
+  <si>
+    <t>FRLMHeaderDocument.documentReference.targetDocument[x]</t>
+  </si>
+  <si>
+    <t>Identifier
+Reference</t>
+  </si>
+  <si>
+    <t>Document cible de la relation, référencé par son identifiant ou par référence directe.</t>
   </si>
 </sst>
 </file>
@@ -754,11 +799,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ23"/>
+  <dimension ref="A1:AJ27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.04296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="51.04296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -781,14 +826,14 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="31.5234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.8671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="51.04296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -3106,6 +3151,406 @@
         <v>72</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
